--- a/attached_assets/Portal_Data_Latest.xlsx
+++ b/attached_assets/Portal_Data_Latest.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5211" uniqueCount="5211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="5269">
   <si>
     <t>HQ Country</t>
   </si>
@@ -714,7 +714,7 @@
     <t>ADARGA LIMITED</t>
   </si>
   <si>
-    <t>14/10 - Adarga messaged back, arranging a slot to present</t>
+    <t>29/10 - Meeting booked for 04/11</t>
   </si>
   <si>
     <t>Third Floor Gateway House, Tollgate, Chandlers Ford, Hampshire, United Kingdom, SO53 3TG</t>
@@ -1077,7 +1077,7 @@
     <t>AKAMAI TECHNOLOGIES LIMITED</t>
   </si>
   <si>
-    <t>14/10 - InMail sent to right contact, awaiting response, team are at an event this week in so may be a delay in response.</t>
+    <t>29/10 - awaiting best contact in UK/I</t>
   </si>
   <si>
     <t>GB 753 2393 88</t>
@@ -4350,7 +4350,7 @@
     <t>COREWEAVE UK LIMITED</t>
   </si>
   <si>
-    <t xml:space="preserve">15/10 - Internal meeting to identify key UKI contacts and arrange meeting to align. </t>
+    <t xml:space="preserve">29/10 - engaged with UK/I procurement and global supply chain team. </t>
   </si>
   <si>
     <t>www.coreweave.com</t>
@@ -6873,7 +6873,7 @@
     <t>GCORE TECHNOLOGIES UK LIMITED</t>
   </si>
   <si>
-    <t>10/10 - Nscale engaged</t>
+    <t xml:space="preserve">29/10 - Engaged with Global PR and Communications lead based in the UK. Arranging sync up with relevant teams. </t>
   </si>
   <si>
     <t>www.gcore.com</t>
@@ -15680,6 +15680,180 @@
   </si>
   <si>
     <t>27/10 - added following information from David G on team call</t>
+  </si>
+  <si>
+    <t>5C.ai</t>
+  </si>
+  <si>
+    <t>5C GROUP LTD</t>
+  </si>
+  <si>
+    <t>29/10 - Contact C Level via LinkedIn</t>
+  </si>
+  <si>
+    <t>Abtec Network Systems</t>
+  </si>
+  <si>
+    <t>ABTEC NETWORK SYSTEMS LTD</t>
+  </si>
+  <si>
+    <t>AI Pathfinder</t>
+  </si>
+  <si>
+    <t>AI PATHFINDER LTD</t>
+  </si>
+  <si>
+    <t>Asanti</t>
+  </si>
+  <si>
+    <t>ASANTI DATACENTRE LIMITED</t>
+  </si>
+  <si>
+    <t>Atlantis Computing UK</t>
+  </si>
+  <si>
+    <t>ATLANTIS COMPUTING LIMITED</t>
+  </si>
+  <si>
+    <t>BE (British Electric)</t>
+  </si>
+  <si>
+    <t>BRITISH ELECTRIC INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Boston Limited</t>
+  </si>
+  <si>
+    <t>Broadberry Data Systems</t>
+  </si>
+  <si>
+    <t>BROADBERRY DATA SYSTEMS LIMITED</t>
+  </si>
+  <si>
+    <t>Captec Group</t>
+  </si>
+  <si>
+    <t>CAPTEC GROUP PLC</t>
+  </si>
+  <si>
+    <t>Cloud Factory</t>
+  </si>
+  <si>
+    <t>CLOUD FACTORY LIMITED</t>
+  </si>
+  <si>
+    <t>CloudCoCo</t>
+  </si>
+  <si>
+    <t>CLOUDCOCO GROUP PLC</t>
+  </si>
+  <si>
+    <t>Critical Network Infra</t>
+  </si>
+  <si>
+    <t>CRITICAL NETWORK INFRASTRUCTURE LTD</t>
+  </si>
+  <si>
+    <t>DeepScience Ventures</t>
+  </si>
+  <si>
+    <t>DEEP SCIENCE VENTURES LTD</t>
+  </si>
+  <si>
+    <t>eta Compute Ltd</t>
+  </si>
+  <si>
+    <t>ETA COMPUTE LIMITED</t>
+  </si>
+  <si>
+    <t>Exertis Hammer</t>
+  </si>
+  <si>
+    <t>EXERTIS HAMMER LIMITED</t>
+  </si>
+  <si>
+    <t>HyperCloud for AI &amp; Analytics</t>
+  </si>
+  <si>
+    <t>HYPERCLOUD LTD / HYPERCLOUD SYSTEMS LTD</t>
+  </si>
+  <si>
+    <t>Keysource</t>
+  </si>
+  <si>
+    <t>KEYSOURCE LIMITED</t>
+  </si>
+  <si>
+    <t>Krome Technologies</t>
+  </si>
+  <si>
+    <t>KROME TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>M2M Direct</t>
+  </si>
+  <si>
+    <t>M2M DIRECT LTD</t>
+  </si>
+  <si>
+    <t>Node4</t>
+  </si>
+  <si>
+    <t>Novatech</t>
+  </si>
+  <si>
+    <t>NOVATECH LIMITED</t>
+  </si>
+  <si>
+    <t>Ori Industries</t>
+  </si>
+  <si>
+    <t>ORI INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Phoenix Datacom</t>
+  </si>
+  <si>
+    <t>PHOENIX DATACOM LTD</t>
+  </si>
+  <si>
+    <t>Proact IT</t>
+  </si>
+  <si>
+    <t>PROACT IT UK LTD</t>
+  </si>
+  <si>
+    <t>QTS Data Centers UK</t>
+  </si>
+  <si>
+    <t>QTS UK LIMITED</t>
+  </si>
+  <si>
+    <t>Strawberry Global</t>
+  </si>
+  <si>
+    <t>STRAWBERRY GLOBAL LTD</t>
+  </si>
+  <si>
+    <t>Sudlows</t>
+  </si>
+  <si>
+    <t>SUDLOWS LIMITED</t>
+  </si>
+  <si>
+    <t>Transparity</t>
+  </si>
+  <si>
+    <t>UKFast</t>
+  </si>
+  <si>
+    <t>UKFAST.NET LIMITED</t>
+  </si>
+  <si>
+    <t>Vespertec</t>
+  </si>
+  <si>
+    <t>VESPERTEC LTD</t>
   </si>
 </sst>
 </file>
@@ -16121,7 +16295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT742"/>
+  <dimension ref="A1:AT772"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.0296964645386" customWidth="1"/>
@@ -17238,9 +17412,6 @@
       <c r="H13" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="J13" s="0">
         <v>5748868</v>
       </c>
@@ -76544,6 +76715,426 @@
       </c>
       <c r="S742" s="0" t="s">
         <v>3259</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="E743" s="0" t="s">
+        <v>5211</v>
+      </c>
+      <c r="F743" s="0" t="s">
+        <v>5212</v>
+      </c>
+      <c r="H743" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I743" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="E744" s="0" t="s">
+        <v>5214</v>
+      </c>
+      <c r="F744" s="0" t="s">
+        <v>5215</v>
+      </c>
+      <c r="H744" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I744" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="E745" s="0" t="s">
+        <v>5216</v>
+      </c>
+      <c r="F745" s="0" t="s">
+        <v>5217</v>
+      </c>
+      <c r="H745" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I745" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="E746" s="0" t="s">
+        <v>5218</v>
+      </c>
+      <c r="F746" s="0" t="s">
+        <v>5219</v>
+      </c>
+      <c r="H746" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I746" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="E747" s="0" t="s">
+        <v>5220</v>
+      </c>
+      <c r="F747" s="0" t="s">
+        <v>5221</v>
+      </c>
+      <c r="H747" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I747" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="E748" s="0" t="s">
+        <v>5222</v>
+      </c>
+      <c r="F748" s="0" t="s">
+        <v>5223</v>
+      </c>
+      <c r="H748" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I748" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="E749" s="0" t="s">
+        <v>5224</v>
+      </c>
+      <c r="F749" s="0" t="s">
+        <v>800</v>
+      </c>
+      <c r="H749" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I749" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="E750" s="0" t="s">
+        <v>5225</v>
+      </c>
+      <c r="F750" s="0" t="s">
+        <v>5226</v>
+      </c>
+      <c r="H750" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I750" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="E751" s="0" t="s">
+        <v>5227</v>
+      </c>
+      <c r="F751" s="0" t="s">
+        <v>5228</v>
+      </c>
+      <c r="H751" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I751" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="E752" s="0" t="s">
+        <v>5229</v>
+      </c>
+      <c r="F752" s="0" t="s">
+        <v>5230</v>
+      </c>
+      <c r="H752" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I752" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="E753" s="0" t="s">
+        <v>5231</v>
+      </c>
+      <c r="F753" s="0" t="s">
+        <v>5232</v>
+      </c>
+      <c r="H753" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I753" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="E754" s="0" t="s">
+        <v>5233</v>
+      </c>
+      <c r="F754" s="0" t="s">
+        <v>5234</v>
+      </c>
+      <c r="H754" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I754" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="E755" s="0" t="s">
+        <v>5235</v>
+      </c>
+      <c r="F755" s="0" t="s">
+        <v>5236</v>
+      </c>
+      <c r="H755" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I755" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="E756" s="0" t="s">
+        <v>5237</v>
+      </c>
+      <c r="F756" s="0" t="s">
+        <v>5238</v>
+      </c>
+      <c r="H756" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I756" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="E757" s="0" t="s">
+        <v>5239</v>
+      </c>
+      <c r="F757" s="0" t="s">
+        <v>5240</v>
+      </c>
+      <c r="H757" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I757" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="E758" s="0" t="s">
+        <v>5241</v>
+      </c>
+      <c r="F758" s="0" t="s">
+        <v>5242</v>
+      </c>
+      <c r="H758" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I758" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="E759" s="0" t="s">
+        <v>5243</v>
+      </c>
+      <c r="F759" s="0" t="s">
+        <v>5244</v>
+      </c>
+      <c r="H759" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I759" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="E760" s="0" t="s">
+        <v>5245</v>
+      </c>
+      <c r="F760" s="0" t="s">
+        <v>5246</v>
+      </c>
+      <c r="H760" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I760" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="E761" s="0" t="s">
+        <v>5247</v>
+      </c>
+      <c r="F761" s="0" t="s">
+        <v>5248</v>
+      </c>
+      <c r="H761" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I761" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="E762" s="0" t="s">
+        <v>5249</v>
+      </c>
+      <c r="F762" s="0" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H762" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I762" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="E763" s="0" t="s">
+        <v>5250</v>
+      </c>
+      <c r="F763" s="0" t="s">
+        <v>5251</v>
+      </c>
+      <c r="H763" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I763" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="E764" s="0" t="s">
+        <v>5252</v>
+      </c>
+      <c r="F764" s="0" t="s">
+        <v>5253</v>
+      </c>
+      <c r="H764" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I764" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="E765" s="0" t="s">
+        <v>5254</v>
+      </c>
+      <c r="F765" s="0" t="s">
+        <v>5255</v>
+      </c>
+      <c r="H765" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I765" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="E766" s="0" t="s">
+        <v>5256</v>
+      </c>
+      <c r="F766" s="0" t="s">
+        <v>5257</v>
+      </c>
+      <c r="H766" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I766" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="E767" s="0" t="s">
+        <v>5258</v>
+      </c>
+      <c r="F767" s="0" t="s">
+        <v>5259</v>
+      </c>
+      <c r="H767" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I767" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="E768" s="0" t="s">
+        <v>5260</v>
+      </c>
+      <c r="F768" s="0" t="s">
+        <v>5261</v>
+      </c>
+      <c r="H768" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I768" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="E769" s="0" t="s">
+        <v>5262</v>
+      </c>
+      <c r="F769" s="0" t="s">
+        <v>5263</v>
+      </c>
+      <c r="H769" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I769" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="E770" s="0" t="s">
+        <v>5264</v>
+      </c>
+      <c r="F770" s="0" t="s">
+        <v>4455</v>
+      </c>
+      <c r="H770" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I770" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="E771" s="0" t="s">
+        <v>5265</v>
+      </c>
+      <c r="F771" s="0" t="s">
+        <v>5266</v>
+      </c>
+      <c r="H771" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I771" s="0" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="E772" s="0" t="s">
+        <v>5267</v>
+      </c>
+      <c r="F772" s="0" t="s">
+        <v>5268</v>
+      </c>
+      <c r="H772" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I772" s="0" t="s">
+        <v>5213</v>
       </c>
     </row>
   </sheetData>

--- a/attached_assets/Portal_Data_Latest.xlsx
+++ b/attached_assets/Portal_Data_Latest.xlsx
@@ -714,7 +714,7 @@
     <t>ADARGA LIMITED</t>
   </si>
   <si>
-    <t>29/10 - Meeting booked for 04/11</t>
+    <t>08/10 - awaiting NDA signature for meeting mid November</t>
   </si>
   <si>
     <t>Third Floor Gateway House, Tollgate, Chandlers Ford, Hampshire, United Kingdom, SO53 3TG</t>

--- a/attached_assets/Portal_Data_Latest.xlsx
+++ b/attached_assets/Portal_Data_Latest.xlsx
@@ -714,7 +714,7 @@
     <t>ADARGA LIMITED</t>
   </si>
   <si>
-    <t>08/10 - awaiting NDA signature for meeting mid November</t>
+    <t>08/11 - awaiting NDA signature for meeting mid November</t>
   </si>
   <si>
     <t>Third Floor Gateway House, Tollgate, Chandlers Ford, Hampshire, United Kingdom, SO53 3TG</t>

--- a/attached_assets/Portal_Data_Latest.xlsx
+++ b/attached_assets/Portal_Data_Latest.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5405" uniqueCount="5405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5385" uniqueCount="5385">
   <si>
     <t>HQ Country</t>
   </si>
@@ -15674,22 +15674,34 @@
     <t>Full Stack Provider</t>
   </si>
   <si>
-    <t>5C.ai</t>
-  </si>
-  <si>
     <t>5C GROUP LTD</t>
   </si>
   <si>
     <t>29/10 - Contact C Level via LinkedIn</t>
   </si>
   <si>
+    <t>Damer House, Meadow Way, Wickford, Essex, SS12 9HA</t>
+  </si>
+  <si>
+    <t>SS12 9HA</t>
+  </si>
+  <si>
     <t>The "AI" name suggests a core focus on AI development, likely needing SLM capabilities.</t>
   </si>
   <si>
     <t>(ML, DEV, TUN, INF) As a core AI company, they are a prime customer for the full lifecycle of model development and deployment.</t>
   </si>
   <si>
-    <t>OPER8 GLOBAL</t>
+    <t>ABTEC NETWORK SYSTEMS LTD</t>
+  </si>
+  <si>
+    <t>ABTEC NETWORK SYSTEMS LTD.</t>
+  </si>
+  <si>
+    <t>Barents House, Compass Point, Market Harborough, Leics, LE16 9HW</t>
+  </si>
+  <si>
+    <t>LE16 9HW</t>
   </si>
   <si>
     <t>A data centre hardware and services provider; a supplier/channel, not a direct end-user.</t>
@@ -15701,10 +15713,13 @@
     <t>(N/A) A data centre supplier, not a user of AI compute services.</t>
   </si>
   <si>
-    <t>Abtec Network Systems</t>
-  </si>
-  <si>
-    <t>ABTEC NETWORK SYSTEMS LTD</t>
+    <t>AI PATHFINDER LTD</t>
+  </si>
+  <si>
+    <t>10 Pipkin Drive, Buntingford, SG9 9FU</t>
+  </si>
+  <si>
+    <t>SG9 9FU</t>
   </si>
   <si>
     <t>A network cabling and infrastructure installer; a supplier, not an end-user of SLMs.</t>
@@ -15716,7 +15731,10 @@
     <t>(N/A) A physical infrastructure installer, not a user of AI compute services.</t>
   </si>
   <si>
-    <t>STAR EUROPE LIMITED</t>
+    <t>ASANTI DATACENTRE LIMITED</t>
+  </si>
+  <si>
+    <t>4 Lister Way, Hamilton International Technology Park, Blantyre, South Lanarkshire, G72 0FT</t>
   </si>
   <si>
     <t>An IT hardware distributor; part of the supply chain, not a direct SLM user.</t>
@@ -15725,10 +15743,19 @@
     <t>(N/A) A hardware distributor, not a user of AI compute services.</t>
   </si>
   <si>
-    <t>AI Pathfinder</t>
-  </si>
-  <si>
-    <t>AI PATHFINDER LTD</t>
+    <t>ATLANTIS COMPUTING LIMITED</t>
+  </si>
+  <si>
+    <t>ATLANTIS COMPUTING LTD</t>
+  </si>
+  <si>
+    <t>SC342890</t>
+  </si>
+  <si>
+    <t>15 Parkdyke, Stirling, Stirlingshire, FK7 9LR</t>
+  </si>
+  <si>
+    <t>FK7 9LR</t>
   </si>
   <si>
     <t>An AI consultancy that would be heavily involved in advising on and integrating SLM solutions.</t>
@@ -15737,34 +15764,46 @@
     <t>(DEV, TUN) A prime partner to use Nscale for building, testing, and fine-tuning AI solutions for their clients.</t>
   </si>
   <si>
-    <t>DCS</t>
+    <t>Unit 5, Curo Park, Frogmore, St. Albans, Hertfordshire, AL2 2DD</t>
   </si>
   <si>
     <t>(Assuming Data Centre Solutions) A data centre design/build specialist; a supplier, not an end-user.</t>
   </si>
   <si>
-    <t>Asanti</t>
-  </si>
-  <si>
-    <t>ASANTI DATACENTRE LIMITED</t>
+    <t>BROADBERRY DATA SYSTEMS LIMITED</t>
+  </si>
+  <si>
+    <t>Belmont House, Belmont Road, Uxbridge, UB8 1HE</t>
+  </si>
+  <si>
+    <t>UB8 1HE</t>
   </si>
   <si>
     <t>A data centre operator (colocation), providing the physical environment for SLM infrastructure.</t>
   </si>
   <si>
-    <t>DS TOTAL SOLUTIONS LTD</t>
+    <t>CAPTEC GROUP PLC</t>
+  </si>
+  <si>
+    <t>7 Whittle Avenue, Fareham, Hampshire, PO15 5SH</t>
+  </si>
+  <si>
+    <t>PO15 5SH</t>
   </si>
   <si>
     <t>A general IT solutions provider, a potential integrator of SLM services for SMEs.</t>
   </si>
   <si>
-    <t>Atlantis Computing UK</t>
-  </si>
-  <si>
-    <t>ATLANTIS COMPUTING LIMITED</t>
-  </si>
-  <si>
-    <t>SC342890</t>
+    <t>CLOUD FACTORY LIMITED</t>
+  </si>
+  <si>
+    <t>CLOUD FACTORY LTD</t>
+  </si>
+  <si>
+    <t>11 Main Street, Barkby, Leicester, LE7 3QG</t>
+  </si>
+  <si>
+    <t>LE7 3QG</t>
   </si>
   <si>
     <t>A niche IT solutions provider; not a primary target but may have specific projects.</t>
@@ -15776,7 +15815,10 @@
     <t>(DEV) Might use an AI platform for specific R&amp;D or client PoCs.</t>
   </si>
   <si>
-    <t>PUREVPS LTD.</t>
+    <t>CLOUDCOCO GROUP PLC</t>
+  </si>
+  <si>
+    <t>5 Fleet Place, London, EC4M 7RD</t>
   </si>
   <si>
     <t>A VPS hosting provider that may be expanding into offering GPU instances for SLM inference.</t>
@@ -15785,10 +15827,16 @@
     <t>(INF, DEV) Could use Nscale to augment its own GPU offerings or for internal development.</t>
   </si>
   <si>
-    <t>BE (British Electric)</t>
-  </si>
-  <si>
-    <t>BRITISH ELECTRIC INFRASTRUCTURE LIMITED</t>
+    <t>DEEP SCIENCE VENTURES LTD</t>
+  </si>
+  <si>
+    <t>DEEP SCIENCE VENTURES LIMITED</t>
+  </si>
+  <si>
+    <t>Taylor Viney &amp; Marlow, 46-54 High Street, Ingatestone, Essex, CM4 9DW</t>
+  </si>
+  <si>
+    <t>CM4 9DW</t>
   </si>
   <si>
     <t>A large-scale infrastructure developer (power/fibre), enabling the next wave of AI data centres.</t>
@@ -15800,7 +15848,13 @@
     <t>(N/A) An infrastructure builder, not a consumer of AI compute services.</t>
   </si>
   <si>
-    <t>NET AI</t>
+    <t>EXERTIS HAMMER LIMITED</t>
+  </si>
+  <si>
+    <t>Vision 27 Stewart Road, Basingstoke, RG24 8NF</t>
+  </si>
+  <si>
+    <t>RG24 8NF</t>
   </si>
   <si>
     <t>An AI company focused on network operations, a prime user of SLMs for network analysis.</t>
@@ -15809,7 +15863,13 @@
     <t>(ML, DEV, INF) A strong candidate for training and deploying models for network traffic analysis and optimisation.</t>
   </si>
   <si>
-    <t>Boston Limited</t>
+    <t>HYPERCLOUD LTD / HYPERCLOUD SYSTEMS LTD</t>
+  </si>
+  <si>
+    <t>HYPERCLOUD SYSTEMS LTD</t>
+  </si>
+  <si>
+    <t>Building 6000 Langstone Technology Park Langstone Road, Havant, Hampshire, PO9 1SA</t>
   </si>
   <si>
     <t>A key HPC/AI hardware integrator and partner, building the clusters that run SLMs.</t>
@@ -15818,16 +15878,28 @@
     <t>(DEV) Would use Nscale for benchmarking, testing, and building customer proofs-of-concept.</t>
   </si>
   <si>
-    <t>UKAI</t>
+    <t>KEYSOURCE LIMITED</t>
+  </si>
+  <si>
+    <t>3 City Place Beehive Ring Road, London Gatwick Airport, Gatwick, RH6 0PA</t>
+  </si>
+  <si>
+    <t>RH6 0PA</t>
   </si>
   <si>
     <t>(Assuming UK AI Ltd) A core AI company, making them a prime user of SLM technology.</t>
   </si>
   <si>
-    <t>Broadberry Data Systems</t>
-  </si>
-  <si>
-    <t>BROADBERRY DATA SYSTEMS LIMITED</t>
+    <t>KROME TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>KROME TECHNOLOGIES LTD</t>
+  </si>
+  <si>
+    <t>Krome House, Pound Road, Chertsey, KT16 8ER</t>
+  </si>
+  <si>
+    <t>KT16 8ER</t>
   </si>
   <si>
     <t>A server and storage hardware builder, a key supplier for SLM infrastructure.</t>
@@ -15836,19 +15908,19 @@
     <t>(DEV) Would use Nscale for internal R&amp;D, benchmarking, and building customer proofs-of-concept.</t>
   </si>
   <si>
-    <t>KUBUS GROUP LTD</t>
-  </si>
-  <si>
     <t>A software provider for the construction (BIM) sector; a good candidate for integrating SLMs.</t>
   </si>
   <si>
     <t>(DEV, TUN, INF) A candidate for training models on design and engineering data to add features to their software.</t>
   </si>
   <si>
-    <t>Captec Group</t>
-  </si>
-  <si>
-    <t>CAPTEC GROUP PLC</t>
+    <t>NOVATECH LIMITED</t>
+  </si>
+  <si>
+    <t>Harbour House, Hamilton Road Cosham, Portsmouth, Hampshire, PO6 4PU</t>
+  </si>
+  <si>
+    <t>PO6 4PU</t>
   </si>
   <si>
     <t>A specialist industrial computer hardware manufacturer; could use SLMs for edge AI.</t>
@@ -15860,7 +15932,10 @@
     <t>(DEV, INF) Could use Nscale to develop and test models that are ultimately deployed on their edge hardware.</t>
   </si>
   <si>
-    <t>FLEXGRID</t>
+    <t>ORI INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Tintagel House, Albert Embankment, London, SE1 7TY</t>
   </si>
   <si>
     <t>A smart energy/grid technology company, a prime user of AI for optimisation and forecasting.</t>
@@ -15872,10 +15947,16 @@
     <t>(ML, DEV, INF) A strong candidate for training models on energy grid data for forecasting and optimisation.</t>
   </si>
   <si>
-    <t>Cloud Factory</t>
-  </si>
-  <si>
-    <t>CLOUD FACTORY LIMITED</t>
+    <t>PHOENIX DATACOM LTD</t>
+  </si>
+  <si>
+    <t>PHOENIX DATACOM LIMITED</t>
+  </si>
+  <si>
+    <t>Phoenix House, Smeaton Close, Rabans Lane, Aylesbury, Buckinghamshire, HP19 8UW</t>
+  </si>
+  <si>
+    <t>HP19 8UW</t>
   </si>
   <si>
     <t>A leading data annotation ("data-labeling-as-a-service") company, critical to the SLM pipeline.</t>
@@ -15884,16 +15965,28 @@
     <t>(DEV, TUN) A prime candidate to use Nscale to develop AI models that automate their own data annotation processes.</t>
   </si>
   <si>
-    <t>NEUTRALITY MANAGED SERVICES</t>
+    <t>PROACT IT UK LTD</t>
+  </si>
+  <si>
+    <t>Grayson House, Venture Way, Chesterfield, Derbyshire, S41 8NE</t>
+  </si>
+  <si>
+    <t>S41 8NE</t>
   </si>
   <si>
     <t>A general IT managed service provider, likely a reseller of SLM services rather than a user.</t>
   </si>
   <si>
-    <t>CloudCoCo</t>
-  </si>
-  <si>
-    <t>CLOUDCOCO GROUP PLC</t>
+    <t>QTS UK LIMITED</t>
+  </si>
+  <si>
+    <t>Q.T.S. (UK) LIMITED</t>
+  </si>
+  <si>
+    <t>Unit 1a Stillington Industrial Estate, Stillington, Stockton-On-Tees, Cleveland, TS21 1AF</t>
+  </si>
+  <si>
+    <t>TS21 1AF</t>
   </si>
   <si>
     <t>A managed service provider that will likely integrate SLM solutions for its customer base.</t>
@@ -15902,16 +15995,28 @@
     <t>(DEV, INF) Could use Nscale to build and offer niche AI services to its client base.</t>
   </si>
   <si>
-    <t>SCALEWAY</t>
+    <t>STRAWBERRY GLOBAL LTD</t>
+  </si>
+  <si>
+    <t>STRAWBERRY GLOBAL TECHNOLOGY LIMITED</t>
+  </si>
+  <si>
+    <t>8 Waldegrave Road, Suite 7, 2nd Floor, Teddington, TW11 8GT</t>
+  </si>
+  <si>
+    <t>TW11 8GT</t>
   </si>
   <si>
     <t>A major European cloud provider offering a full suite of services, including GPU instances.</t>
   </si>
   <si>
-    <t>Critical Network Infra</t>
-  </si>
-  <si>
-    <t>CRITICAL NETWORK INFRASTRUCTURE LTD</t>
+    <t>SUDLOWS LIMITED</t>
+  </si>
+  <si>
+    <t>Ducie Works, Hulme Hall Lane, Manchester, Lancashire, M40 8HH</t>
+  </si>
+  <si>
+    <t>M40 8HH</t>
   </si>
   <si>
     <t>A specialist network infrastructure provider, a key enabler but not a direct SLM user.</t>
@@ -15923,16 +16028,19 @@
     <t>(N/A) An infrastructure provider, not a consumer of AI compute services.</t>
   </si>
   <si>
-    <t>RETN</t>
+    <t>2 Kingdom Street, Paddington, London, W2 6BD</t>
   </si>
   <si>
     <t>An international network provider, a key consumer of DCI to connect data centres globally.</t>
   </si>
   <si>
-    <t>DeepScience Ventures</t>
-  </si>
-  <si>
-    <t>DEEP SCIENCE VENTURES LTD</t>
+    <t>UKFAST.NET LIMITED</t>
+  </si>
+  <si>
+    <t>ANS ACADEMY LIMITED</t>
+  </si>
+  <si>
+    <t>1 Archway, Manchester, M15 5QJ</t>
   </si>
   <si>
     <t>A venture capital firm/incubator; their portfolio companies are the prospects, not the VC itself.</t>
@@ -15941,7 +16049,16 @@
     <t>(DEV, ML) The VC itself might use Nscale to provide a development sandbox for its portfolio of early-stage AI companies.</t>
   </si>
   <si>
-    <t>G42</t>
+    <t>VESPERTEC LTD</t>
+  </si>
+  <si>
+    <t>VESPERTECH LTD.</t>
+  </si>
+  <si>
+    <t>82 Coleburn Road, Norwich, NR1 2NZ</t>
+  </si>
+  <si>
+    <t>NR1 2NZ</t>
   </si>
   <si>
     <t>A major global AI and cloud computing company with massive investment in model training.</t>
@@ -15953,18 +16070,6 @@
     <t>(ML, DEV, TUN, INF) A primary customer/partner for large-scale model training, development, and deployment.</t>
   </si>
   <si>
-    <t>eta Compute Ltd</t>
-  </si>
-  <si>
-    <t>ETA COMPUTE LIMITED</t>
-  </si>
-  <si>
-    <t>(If active) An edge AI chip company, requiring SLM development for their hardware.</t>
-  </si>
-  <si>
-    <t>(DEV, TUN) Would use Nscale to develop and fine-tune models to run optimally on their low-power edge chips.</t>
-  </si>
-  <si>
     <t>FREECLIX LTD</t>
   </si>
   <si>
@@ -15977,15 +16082,6 @@
     <t>(N/A) A network provider, not a consumer of AI compute services.</t>
   </si>
   <si>
-    <t>Exertis Hammer</t>
-  </si>
-  <si>
-    <t>EXERTIS HAMMER LIMITED</t>
-  </si>
-  <si>
-    <t>A value-added distributor, a key channel partner but not an end-user of SLMs.</t>
-  </si>
-  <si>
     <t>HARDY FISHER SERVICES LIMITED</t>
   </si>
   <si>
@@ -15995,90 +16091,39 @@
     <t>(N/A) A data centre consultancy, not a user of AI compute services.</t>
   </si>
   <si>
-    <t>HyperCloud for AI &amp; Analytics</t>
-  </si>
-  <si>
-    <t>HYPERCLOUD LTD / HYPERCLOUD SYSTEMS LTD</t>
-  </si>
-  <si>
-    <t>The name implies a direct focus on providing an AI cloud platform.</t>
+    <t>AMATIS NETWORKS</t>
+  </si>
+  <si>
+    <t>A cloud and connectivity provider that may be expanding into SLM services.</t>
+  </si>
+  <si>
+    <t>DATACENTREPLUS</t>
+  </si>
+  <si>
+    <t>A regional colocation provider, providing the physical environment for SLM infrastructure.</t>
+  </si>
+  <si>
+    <t>HOSTKEY</t>
+  </si>
+  <si>
+    <t>A GPU dedicated server and cloud provider, a prime candidate for all SLM services.</t>
+  </si>
+  <si>
+    <t>As a GPU-focused IaaS provider, they are a primary direct purchaser of high-performance DCF for their data centres.</t>
+  </si>
+  <si>
+    <t>HYPERSTACK CLOUD</t>
+  </si>
+  <si>
+    <t>A cloud provider with a clear focus on high-performance compute, likely including GPUs.</t>
+  </si>
+  <si>
+    <t>As a performance-focused cloud provider, they are a primary direct purchaser of high-performance DCF.</t>
   </si>
   <si>
     <t>(ML, INF, DEV, TUN) A prime candidate for the full suite of AI services, or a potential partner/competitor.</t>
   </si>
   <si>
-    <t>AMATIS NETWORKS</t>
-  </si>
-  <si>
-    <t>A cloud and connectivity provider that may be expanding into SLM services.</t>
-  </si>
-  <si>
-    <t>Keysource</t>
-  </si>
-  <si>
-    <t>KEYSOURCE LIMITED</t>
-  </si>
-  <si>
-    <t>A data centre design and operations consultancy; an influencer, not a direct user.</t>
-  </si>
-  <si>
-    <t>DATACENTREPLUS</t>
-  </si>
-  <si>
-    <t>A regional colocation provider, providing the physical environment for SLM infrastructure.</t>
-  </si>
-  <si>
-    <t>Krome Technologies</t>
-  </si>
-  <si>
-    <t>KROME TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>An IT infrastructure reseller and managed service provider; a channel partner.</t>
-  </si>
-  <si>
-    <t>An integrator and channel partner, not a direct end-consumer for its own use.</t>
-  </si>
-  <si>
-    <t>HOSTKEY</t>
-  </si>
-  <si>
-    <t>A GPU dedicated server and cloud provider, a prime candidate for all SLM services.</t>
-  </si>
-  <si>
-    <t>As a GPU-focused IaaS provider, they are a primary direct purchaser of high-performance DCF for their data centres.</t>
-  </si>
-  <si>
-    <t>M2M Direct</t>
-  </si>
-  <si>
-    <t>M2M DIRECT LTD</t>
-  </si>
-  <si>
-    <t>An IT hardware reseller, part of the supply chain, not a direct SLM user.</t>
-  </si>
-  <si>
-    <t>A reseller, part of the supply chain and not an end-user of data centre networking.</t>
-  </si>
-  <si>
-    <t>HYPERSTACK CLOUD</t>
-  </si>
-  <si>
-    <t>A cloud provider with a clear focus on high-performance compute, likely including GPUs.</t>
-  </si>
-  <si>
-    <t>As a performance-focused cloud provider, they are a primary direct purchaser of high-performance DCF.</t>
-  </si>
-  <si>
-    <t>Node4</t>
-  </si>
-  <si>
-    <t>A major UK managed service and cloud provider with its own data centres, a strong SLM prospect.</t>
-  </si>
-  <si>
-    <t>(DEV, INF) A major managed cloud provider that would use Nscale to build and host AI solutions for UK businesses.</t>
-  </si>
-  <si>
     <t>OTTER AI</t>
   </si>
   <si>
@@ -16091,15 +16136,6 @@
     <t>(ML, TUN, INF) A core AI company with a constant need for large-scale, low-latency inference and model fine-tuning.</t>
   </si>
   <si>
-    <t>Novatech</t>
-  </si>
-  <si>
-    <t>NOVATECH LIMITED</t>
-  </si>
-  <si>
-    <t>An IT hardware manufacturer (workstations, servers) and reseller.</t>
-  </si>
-  <si>
     <t>PIXIS</t>
   </si>
   <si>
@@ -16109,18 +16145,6 @@
     <t>(ML, TUN, INF) A prime customer for training and fine-tuning models on marketing data and running real-time inference.</t>
   </si>
   <si>
-    <t>Ori Industries</t>
-  </si>
-  <si>
-    <t>ORI INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>An edge computing platform, a key enabler for distributed SLM inference.</t>
-  </si>
-  <si>
-    <t>(INF, DEV) A strong candidate for developing and deploying optimised inference models at the edge.</t>
-  </si>
-  <si>
     <t>UNIVERSITY OF BRISTOL (UNITED KINGDOM)</t>
   </si>
   <si>
@@ -16133,21 +16157,6 @@
     <t>(ML, DEV, TUN) A perfect customer for large-scale academic research, model training, and development.</t>
   </si>
   <si>
-    <t>Phoenix Datacom</t>
-  </si>
-  <si>
-    <t>PHOENIX DATACOM LTD</t>
-  </si>
-  <si>
-    <t>A network testing and monitoring reseller; a supplier, not a direct user of SLMs.</t>
-  </si>
-  <si>
-    <t>A reseller/integrator of network tools, not a direct consumer of DCF/DCI for its own operations.</t>
-  </si>
-  <si>
-    <t>(N/A) A test &amp; measurement reseller, not a user of AI compute services.</t>
-  </si>
-  <si>
     <t>ROC TECHNOLOGIES LTD</t>
   </si>
   <si>
@@ -16160,15 +16169,6 @@
     <t>(DEV, INF) Would use Nscale to build and manage AI solutions as part of their client transformation projects.</t>
   </si>
   <si>
-    <t>Proact IT</t>
-  </si>
-  <si>
-    <t>PROACT IT UK LTD</t>
-  </si>
-  <si>
-    <t>(DEV, INF) A major IT provider that would use Nscale to design, build, and manage AI solutions for enterprises.</t>
-  </si>
-  <si>
     <t>TAIGA CLOUD UK LIMITED</t>
   </si>
   <si>
@@ -16179,66 +16179,6 @@
   </si>
   <si>
     <t>(ML, INF, DEV, TUN) A direct competitor and sophisticated user, making them a high-interest strategic account.</t>
-  </si>
-  <si>
-    <t>QTS Data Centers UK</t>
-  </si>
-  <si>
-    <t>QTS UK LIMITED</t>
-  </si>
-  <si>
-    <t>A major hyperscale data centre (colocation) provider, a key enabler for SLM infrastructure.</t>
-  </si>
-  <si>
-    <t>Strawberry Global</t>
-  </si>
-  <si>
-    <t>STRAWBERRY GLOBAL LTD</t>
-  </si>
-  <si>
-    <t>A specialist IT distributor; part of the supply chain, not a direct SLM user.</t>
-  </si>
-  <si>
-    <t>Sudlows</t>
-  </si>
-  <si>
-    <t>SUDLOWS LIMITED</t>
-  </si>
-  <si>
-    <t>A data centre design, build, and maintenance specialist; a supplier, not an end-user.</t>
-  </si>
-  <si>
-    <t>Transparity</t>
-  </si>
-  <si>
-    <t>A Microsoft-focused cloud consultancy, a key partner for integrating Azure-based SLMs.</t>
-  </si>
-  <si>
-    <t>(DEV, TUN) A prime partner to use Nscale to build and fine-tune AI solutions for their Microsoft-centric clients.</t>
-  </si>
-  <si>
-    <t>UKFast</t>
-  </si>
-  <si>
-    <t>UKFAST.NET LIMITED</t>
-  </si>
-  <si>
-    <t>(Now part of ANS) A major UK cloud hosting provider, a strong prospect for SLM services.</t>
-  </si>
-  <si>
-    <t>(DEV, INF) A major managed cloud provider that would use Nscale to build and manage AI solutions for its customers.</t>
-  </si>
-  <si>
-    <t>Vespertec</t>
-  </si>
-  <si>
-    <t>VESPERTEC LTD</t>
-  </si>
-  <si>
-    <t>An IT solutions provider and HPC specialist, a key integrator for SLM deployments.</t>
-  </si>
-  <si>
-    <t>An integrator and channel partner for HPC/AI, not a direct end-consumer for its own use.</t>
   </si>
   <si>
     <t>ITS Technology Group</t>
@@ -16708,7 +16648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT772"/>
+  <dimension ref="A1:AT755"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.0296964645386" customWidth="1"/>
@@ -78331,6 +78271,12 @@
       <c r="E716" s="0" t="s">
         <v>5202</v>
       </c>
+      <c r="G716" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H716" s="0" t="s">
+        <v>151</v>
+      </c>
       <c r="U716" s="0">
         <v>4</v>
       </c>
@@ -78370,7 +78316,7 @@
         <v>5207</v>
       </c>
       <c r="F717" s="0" t="s">
-        <v>5208</v>
+        <v>5207</v>
       </c>
       <c r="G717" s="0" t="s">
         <v>49</v>
@@ -78379,13 +78325,22 @@
         <v>151</v>
       </c>
       <c r="I717" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J717" s="0">
+        <v>8784891</v>
+      </c>
+      <c r="R717" s="0" t="s">
         <v>5209</v>
+      </c>
+      <c r="S717" s="0" t="s">
+        <v>5210</v>
       </c>
       <c r="U717" s="0">
         <v>8</v>
       </c>
       <c r="V717" s="0" t="s">
-        <v>5210</v>
+        <v>5211</v>
       </c>
       <c r="W717" s="0">
         <v>7</v>
@@ -78397,7 +78352,7 @@
         <v>8</v>
       </c>
       <c r="Z717" s="0" t="s">
-        <v>5211</v>
+        <v>5212</v>
       </c>
       <c r="AA717" s="0">
         <v>7.666666666666667</v>
@@ -78414,25 +78369,46 @@
         <v>2</v>
       </c>
       <c r="E718" s="0" t="s">
-        <v>5212</v>
+        <v>5213</v>
+      </c>
+      <c r="F718" s="0" t="s">
+        <v>5214</v>
+      </c>
+      <c r="G718" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H718" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I718" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J718" s="0">
+        <v>3428841</v>
+      </c>
+      <c r="R718" s="0" t="s">
+        <v>5215</v>
+      </c>
+      <c r="S718" s="0" t="s">
+        <v>5216</v>
       </c>
       <c r="U718" s="0">
         <v>4</v>
       </c>
       <c r="V718" s="0" t="s">
-        <v>5213</v>
+        <v>5217</v>
       </c>
       <c r="W718" s="0">
         <v>3</v>
       </c>
       <c r="X718" s="0" t="s">
-        <v>5214</v>
+        <v>5218</v>
       </c>
       <c r="Y718" s="0">
         <v>2</v>
       </c>
       <c r="Z718" s="0" t="s">
-        <v>5215</v>
+        <v>5219</v>
       </c>
       <c r="AA718" s="0">
         <v>3</v>
@@ -78452,10 +78428,10 @@
         <v>2</v>
       </c>
       <c r="E719" s="0" t="s">
-        <v>5216</v>
+        <v>5220</v>
       </c>
       <c r="F719" s="0" t="s">
-        <v>5217</v>
+        <v>5220</v>
       </c>
       <c r="G719" s="0" t="s">
         <v>49</v>
@@ -78464,28 +78440,34 @@
         <v>151</v>
       </c>
       <c r="I719" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="J719" s="0">
-        <v>3428841</v>
+        <v>14988940</v>
+      </c>
+      <c r="R719" s="0" t="s">
+        <v>5221</v>
+      </c>
+      <c r="S719" s="0" t="s">
+        <v>5222</v>
       </c>
       <c r="U719" s="0">
         <v>3</v>
       </c>
       <c r="V719" s="0" t="s">
-        <v>5218</v>
+        <v>5223</v>
       </c>
       <c r="W719" s="0">
         <v>2</v>
       </c>
       <c r="X719" s="0" t="s">
-        <v>5219</v>
+        <v>5224</v>
       </c>
       <c r="Y719" s="0">
         <v>1</v>
       </c>
       <c r="Z719" s="0" t="s">
-        <v>5220</v>
+        <v>5225</v>
       </c>
       <c r="AA719" s="0">
         <v>2</v>
@@ -78502,13 +78484,34 @@
         <v>2</v>
       </c>
       <c r="E720" s="0" t="s">
-        <v>5221</v>
+        <v>5226</v>
+      </c>
+      <c r="F720" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="G720" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H720" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I720" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J720" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="R720" s="0" t="s">
+        <v>5227</v>
+      </c>
+      <c r="S720" s="0" t="s">
+        <v>521</v>
       </c>
       <c r="U720" s="0">
         <v>3</v>
       </c>
       <c r="V720" s="0" t="s">
-        <v>5222</v>
+        <v>5228</v>
       </c>
       <c r="W720" s="0">
         <v>2</v>
@@ -78520,7 +78523,7 @@
         <v>1</v>
       </c>
       <c r="Z720" s="0" t="s">
-        <v>5223</v>
+        <v>5229</v>
       </c>
       <c r="AA720" s="0">
         <v>2</v>
@@ -78540,10 +78543,10 @@
         <v>2</v>
       </c>
       <c r="E721" s="0" t="s">
-        <v>5224</v>
+        <v>5230</v>
       </c>
       <c r="F721" s="0" t="s">
-        <v>5225</v>
+        <v>5231</v>
       </c>
       <c r="G721" s="0" t="s">
         <v>49</v>
@@ -78552,16 +78555,22 @@
         <v>151</v>
       </c>
       <c r="I721" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J721" s="0">
-        <v>14988940</v>
+        <v>5208</v>
+      </c>
+      <c r="J721" s="0" t="s">
+        <v>5232</v>
+      </c>
+      <c r="R721" s="0" t="s">
+        <v>5233</v>
+      </c>
+      <c r="S721" s="0" t="s">
+        <v>5234</v>
       </c>
       <c r="U721" s="0">
         <v>6</v>
       </c>
       <c r="V721" s="0" t="s">
-        <v>5226</v>
+        <v>5235</v>
       </c>
       <c r="W721" s="0">
         <v>4</v>
@@ -78573,7 +78582,7 @@
         <v>7</v>
       </c>
       <c r="Z721" s="0" t="s">
-        <v>5227</v>
+        <v>5236</v>
       </c>
       <c r="AA721" s="0">
         <v>5.666666666666667</v>
@@ -78590,13 +78599,34 @@
         <v>2</v>
       </c>
       <c r="E722" s="0" t="s">
-        <v>5228</v>
+        <v>802</v>
+      </c>
+      <c r="F722" s="0" t="s">
+        <v>802</v>
+      </c>
+      <c r="G722" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H722" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I722" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J722" s="0">
+        <v>2771869</v>
+      </c>
+      <c r="R722" s="0" t="s">
+        <v>5237</v>
+      </c>
+      <c r="S722" s="0" t="s">
+        <v>806</v>
       </c>
       <c r="U722" s="0">
         <v>4</v>
       </c>
       <c r="V722" s="0" t="s">
-        <v>5229</v>
+        <v>5238</v>
       </c>
       <c r="W722" s="0">
         <v>2</v>
@@ -78628,10 +78658,10 @@
         <v>2</v>
       </c>
       <c r="E723" s="0" t="s">
-        <v>5230</v>
+        <v>5239</v>
       </c>
       <c r="F723" s="0" t="s">
-        <v>5231</v>
+        <v>5239</v>
       </c>
       <c r="G723" s="0" t="s">
         <v>49</v>
@@ -78640,16 +78670,22 @@
         <v>151</v>
       </c>
       <c r="I723" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J723" s="0" t="s">
-        <v>517</v>
+        <v>5208</v>
+      </c>
+      <c r="J723" s="0">
+        <v>2882275</v>
+      </c>
+      <c r="R723" s="0" t="s">
+        <v>5240</v>
+      </c>
+      <c r="S723" s="0" t="s">
+        <v>5241</v>
       </c>
       <c r="U723" s="0">
         <v>7</v>
       </c>
       <c r="V723" s="0" t="s">
-        <v>5232</v>
+        <v>5242</v>
       </c>
       <c r="W723" s="0">
         <v>5</v>
@@ -78678,13 +78714,34 @@
         <v>2</v>
       </c>
       <c r="E724" s="0" t="s">
-        <v>5233</v>
+        <v>5243</v>
+      </c>
+      <c r="F724" s="0" t="s">
+        <v>5243</v>
+      </c>
+      <c r="G724" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H724" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I724" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J724" s="0">
+        <v>11281644</v>
+      </c>
+      <c r="R724" s="0" t="s">
+        <v>5244</v>
+      </c>
+      <c r="S724" s="0" t="s">
+        <v>5245</v>
       </c>
       <c r="U724" s="0">
         <v>4</v>
       </c>
       <c r="V724" s="0" t="s">
-        <v>5234</v>
+        <v>5246</v>
       </c>
       <c r="W724" s="0">
         <v>3</v>
@@ -78716,10 +78773,10 @@
         <v>2</v>
       </c>
       <c r="E725" s="0" t="s">
-        <v>5235</v>
+        <v>5247</v>
       </c>
       <c r="F725" s="0" t="s">
-        <v>5236</v>
+        <v>5248</v>
       </c>
       <c r="G725" s="0" t="s">
         <v>49</v>
@@ -78728,28 +78785,34 @@
         <v>151</v>
       </c>
       <c r="I725" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J725" s="0" t="s">
-        <v>5237</v>
+        <v>5208</v>
+      </c>
+      <c r="J725" s="0">
+        <v>15273243</v>
+      </c>
+      <c r="R725" s="0" t="s">
+        <v>5249</v>
+      </c>
+      <c r="S725" s="0" t="s">
+        <v>5250</v>
       </c>
       <c r="U725" s="0">
         <v>4</v>
       </c>
       <c r="V725" s="0" t="s">
-        <v>5238</v>
+        <v>5251</v>
       </c>
       <c r="W725" s="0">
         <v>3</v>
       </c>
       <c r="X725" s="0" t="s">
-        <v>5239</v>
+        <v>5252</v>
       </c>
       <c r="Y725" s="0">
         <v>3</v>
       </c>
       <c r="Z725" s="0" t="s">
-        <v>5240</v>
+        <v>5253</v>
       </c>
       <c r="AA725" s="0">
         <v>3.3333333333333335</v>
@@ -78766,13 +78829,34 @@
         <v>2</v>
       </c>
       <c r="E726" s="0" t="s">
-        <v>5241</v>
+        <v>5254</v>
+      </c>
+      <c r="F726" s="0" t="s">
+        <v>5254</v>
+      </c>
+      <c r="G726" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H726" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I726" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J726" s="0">
+        <v>5259846</v>
+      </c>
+      <c r="R726" s="0" t="s">
+        <v>5255</v>
+      </c>
+      <c r="S726" s="0" t="s">
+        <v>3621</v>
       </c>
       <c r="U726" s="0">
         <v>5</v>
       </c>
       <c r="V726" s="0" t="s">
-        <v>5242</v>
+        <v>5256</v>
       </c>
       <c r="W726" s="0">
         <v>5</v>
@@ -78784,7 +78868,7 @@
         <v>5</v>
       </c>
       <c r="Z726" s="0" t="s">
-        <v>5243</v>
+        <v>5257</v>
       </c>
       <c r="AA726" s="0">
         <v>5</v>
@@ -78804,10 +78888,10 @@
         <v>2</v>
       </c>
       <c r="E727" s="0" t="s">
-        <v>5244</v>
+        <v>5258</v>
       </c>
       <c r="F727" s="0" t="s">
-        <v>5245</v>
+        <v>5259</v>
       </c>
       <c r="G727" s="0" t="s">
         <v>49</v>
@@ -78816,25 +78900,34 @@
         <v>151</v>
       </c>
       <c r="I727" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
+      </c>
+      <c r="J727" s="0">
+        <v>10314171</v>
+      </c>
+      <c r="R727" s="0" t="s">
+        <v>5260</v>
+      </c>
+      <c r="S727" s="0" t="s">
+        <v>5261</v>
       </c>
       <c r="U727" s="0">
         <v>6</v>
       </c>
       <c r="V727" s="0" t="s">
-        <v>5246</v>
+        <v>5262</v>
       </c>
       <c r="W727" s="0">
         <v>6</v>
       </c>
       <c r="X727" s="0" t="s">
-        <v>5247</v>
+        <v>5263</v>
       </c>
       <c r="Y727" s="0">
         <v>2</v>
       </c>
       <c r="Z727" s="0" t="s">
-        <v>5248</v>
+        <v>5264</v>
       </c>
       <c r="AA727" s="0">
         <v>4.666666666666667</v>
@@ -78851,13 +78944,34 @@
         <v>2</v>
       </c>
       <c r="E728" s="0" t="s">
-        <v>5249</v>
+        <v>5265</v>
+      </c>
+      <c r="F728" s="0" t="s">
+        <v>5265</v>
+      </c>
+      <c r="G728" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H728" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I728" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J728" s="0">
+        <v>2640532</v>
+      </c>
+      <c r="R728" s="0" t="s">
+        <v>5266</v>
+      </c>
+      <c r="S728" s="0" t="s">
+        <v>5267</v>
       </c>
       <c r="U728" s="0">
         <v>8</v>
       </c>
       <c r="V728" s="0" t="s">
-        <v>5250</v>
+        <v>5268</v>
       </c>
       <c r="W728" s="0">
         <v>7</v>
@@ -78869,7 +78983,7 @@
         <v>8</v>
       </c>
       <c r="Z728" s="0" t="s">
-        <v>5251</v>
+        <v>5269</v>
       </c>
       <c r="AA728" s="0">
         <v>7.666666666666667</v>
@@ -78889,10 +79003,10 @@
         <v>2</v>
       </c>
       <c r="E729" s="0" t="s">
-        <v>5252</v>
+        <v>5270</v>
       </c>
       <c r="F729" s="0" t="s">
-        <v>802</v>
+        <v>5271</v>
       </c>
       <c r="G729" s="0" t="s">
         <v>49</v>
@@ -78901,16 +79015,22 @@
         <v>151</v>
       </c>
       <c r="I729" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="J729" s="0">
-        <v>2771869</v>
+        <v>14622517</v>
+      </c>
+      <c r="R729" s="0" t="s">
+        <v>5272</v>
+      </c>
+      <c r="S729" s="0" t="s">
+        <v>440</v>
       </c>
       <c r="U729" s="0">
         <v>8</v>
       </c>
       <c r="V729" s="0" t="s">
-        <v>5253</v>
+        <v>5273</v>
       </c>
       <c r="W729" s="0">
         <v>7</v>
@@ -78922,7 +79042,7 @@
         <v>6</v>
       </c>
       <c r="Z729" s="0" t="s">
-        <v>5254</v>
+        <v>5274</v>
       </c>
       <c r="AA729" s="0">
         <v>7</v>
@@ -78939,13 +79059,34 @@
         <v>2</v>
       </c>
       <c r="E730" s="0" t="s">
-        <v>5255</v>
+        <v>5275</v>
+      </c>
+      <c r="F730" s="0" t="s">
+        <v>5275</v>
+      </c>
+      <c r="G730" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H730" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I730" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J730" s="0">
+        <v>3663128</v>
+      </c>
+      <c r="R730" s="0" t="s">
+        <v>5276</v>
+      </c>
+      <c r="S730" s="0" t="s">
+        <v>5277</v>
       </c>
       <c r="U730" s="0">
         <v>8</v>
       </c>
       <c r="V730" s="0" t="s">
-        <v>5256</v>
+        <v>5278</v>
       </c>
       <c r="W730" s="0">
         <v>7</v>
@@ -78957,7 +79098,7 @@
         <v>8</v>
       </c>
       <c r="Z730" s="0" t="s">
-        <v>5211</v>
+        <v>5212</v>
       </c>
       <c r="AA730" s="0">
         <v>7.666666666666667</v>
@@ -78977,10 +79118,10 @@
         <v>2</v>
       </c>
       <c r="E731" s="0" t="s">
-        <v>5257</v>
+        <v>5279</v>
       </c>
       <c r="F731" s="0" t="s">
-        <v>5258</v>
+        <v>5280</v>
       </c>
       <c r="G731" s="0" t="s">
         <v>49</v>
@@ -78989,16 +79130,22 @@
         <v>151</v>
       </c>
       <c r="I731" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="J731" s="0">
-        <v>2882275</v>
+        <v>7031219</v>
+      </c>
+      <c r="R731" s="0" t="s">
+        <v>5281</v>
+      </c>
+      <c r="S731" s="0" t="s">
+        <v>5282</v>
       </c>
       <c r="U731" s="0">
         <v>6</v>
       </c>
       <c r="V731" s="0" t="s">
-        <v>5259</v>
+        <v>5283</v>
       </c>
       <c r="W731" s="0">
         <v>5</v>
@@ -79010,7 +79157,7 @@
         <v>4</v>
       </c>
       <c r="Z731" s="0" t="s">
-        <v>5260</v>
+        <v>5284</v>
       </c>
       <c r="AA731" s="0">
         <v>5</v>
@@ -79027,13 +79174,34 @@
         <v>2</v>
       </c>
       <c r="E732" s="0" t="s">
-        <v>5261</v>
+        <v>3262</v>
+      </c>
+      <c r="F732" s="0" t="s">
+        <v>3263</v>
+      </c>
+      <c r="G732" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H732" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I732" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J732" s="0">
+        <v>4759927</v>
+      </c>
+      <c r="R732" s="0" t="s">
+        <v>3267</v>
+      </c>
+      <c r="S732" s="0" t="s">
+        <v>3268</v>
       </c>
       <c r="U732" s="0">
         <v>5</v>
       </c>
       <c r="V732" s="0" t="s">
-        <v>5262</v>
+        <v>5285</v>
       </c>
       <c r="W732" s="0">
         <v>4</v>
@@ -79045,7 +79213,7 @@
         <v>5</v>
       </c>
       <c r="Z732" s="0" t="s">
-        <v>5263</v>
+        <v>5286</v>
       </c>
       <c r="AA732" s="0">
         <v>4.666666666666667</v>
@@ -79065,10 +79233,10 @@
         <v>2</v>
       </c>
       <c r="E733" s="0" t="s">
-        <v>5264</v>
+        <v>5287</v>
       </c>
       <c r="F733" s="0" t="s">
-        <v>5265</v>
+        <v>5287</v>
       </c>
       <c r="G733" s="0" t="s">
         <v>49</v>
@@ -79077,28 +79245,34 @@
         <v>151</v>
       </c>
       <c r="I733" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="J733" s="0">
-        <v>11281644</v>
+        <v>2605046</v>
+      </c>
+      <c r="R733" s="0" t="s">
+        <v>5288</v>
+      </c>
+      <c r="S733" s="0" t="s">
+        <v>5289</v>
       </c>
       <c r="U733" s="0">
         <v>5</v>
       </c>
       <c r="V733" s="0" t="s">
-        <v>5266</v>
+        <v>5290</v>
       </c>
       <c r="W733" s="0">
         <v>4</v>
       </c>
       <c r="X733" s="0" t="s">
-        <v>5267</v>
+        <v>5291</v>
       </c>
       <c r="Y733" s="0">
         <v>4</v>
       </c>
       <c r="Z733" s="0" t="s">
-        <v>5268</v>
+        <v>5292</v>
       </c>
       <c r="AA733" s="0">
         <v>4.333333333333333</v>
@@ -79115,25 +79289,46 @@
         <v>2</v>
       </c>
       <c r="E734" s="0" t="s">
-        <v>5269</v>
+        <v>5293</v>
+      </c>
+      <c r="F734" s="0" t="s">
+        <v>3428</v>
+      </c>
+      <c r="G734" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H734" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I734" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J734" s="0">
+        <v>11622392</v>
+      </c>
+      <c r="R734" s="0" t="s">
+        <v>5294</v>
+      </c>
+      <c r="S734" s="0" t="s">
+        <v>3431</v>
       </c>
       <c r="U734" s="0">
         <v>6</v>
       </c>
       <c r="V734" s="0" t="s">
-        <v>5270</v>
+        <v>5295</v>
       </c>
       <c r="W734" s="0">
         <v>5</v>
       </c>
       <c r="X734" s="0" t="s">
-        <v>5271</v>
+        <v>5296</v>
       </c>
       <c r="Y734" s="0">
         <v>6</v>
       </c>
       <c r="Z734" s="0" t="s">
-        <v>5272</v>
+        <v>5297</v>
       </c>
       <c r="AA734" s="0">
         <v>5.666666666666667</v>
@@ -79153,10 +79348,10 @@
         <v>2</v>
       </c>
       <c r="E735" s="0" t="s">
-        <v>5273</v>
+        <v>5298</v>
       </c>
       <c r="F735" s="0" t="s">
-        <v>5274</v>
+        <v>5299</v>
       </c>
       <c r="G735" s="0" t="s">
         <v>49</v>
@@ -79165,16 +79360,22 @@
         <v>151</v>
       </c>
       <c r="I735" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="J735" s="0">
-        <v>15273243</v>
+        <v>14249828</v>
+      </c>
+      <c r="R735" s="0" t="s">
+        <v>5300</v>
+      </c>
+      <c r="S735" s="0" t="s">
+        <v>5301</v>
       </c>
       <c r="U735" s="0">
         <v>7</v>
       </c>
       <c r="V735" s="0" t="s">
-        <v>5275</v>
+        <v>5302</v>
       </c>
       <c r="W735" s="0">
         <v>6</v>
@@ -79186,7 +79387,7 @@
         <v>7</v>
       </c>
       <c r="Z735" s="0" t="s">
-        <v>5276</v>
+        <v>5303</v>
       </c>
       <c r="AA735" s="0">
         <v>6.666666666666667</v>
@@ -79203,13 +79404,34 @@
         <v>2</v>
       </c>
       <c r="E736" s="0" t="s">
-        <v>5277</v>
+        <v>5304</v>
+      </c>
+      <c r="F736" s="0" t="s">
+        <v>3581</v>
+      </c>
+      <c r="G736" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H736" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I736" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J736" s="0">
+        <v>3968273</v>
+      </c>
+      <c r="R736" s="0" t="s">
+        <v>5305</v>
+      </c>
+      <c r="S736" s="0" t="s">
+        <v>5306</v>
       </c>
       <c r="U736" s="0">
         <v>4</v>
       </c>
       <c r="V736" s="0" t="s">
-        <v>5278</v>
+        <v>5307</v>
       </c>
       <c r="W736" s="0">
         <v>3</v>
@@ -79241,10 +79463,10 @@
         <v>2</v>
       </c>
       <c r="E737" s="0" t="s">
-        <v>5279</v>
+        <v>5308</v>
       </c>
       <c r="F737" s="0" t="s">
-        <v>5280</v>
+        <v>5309</v>
       </c>
       <c r="G737" s="0" t="s">
         <v>49</v>
@@ -79253,16 +79475,22 @@
         <v>151</v>
       </c>
       <c r="I737" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="J737" s="0">
-        <v>5259846</v>
+        <v>3893266</v>
+      </c>
+      <c r="R737" s="0" t="s">
+        <v>5310</v>
+      </c>
+      <c r="S737" s="0" t="s">
+        <v>5311</v>
       </c>
       <c r="U737" s="0">
         <v>5</v>
       </c>
       <c r="V737" s="0" t="s">
-        <v>5281</v>
+        <v>5312</v>
       </c>
       <c r="W737" s="0">
         <v>4</v>
@@ -79274,7 +79502,7 @@
         <v>4</v>
       </c>
       <c r="Z737" s="0" t="s">
-        <v>5282</v>
+        <v>5313</v>
       </c>
       <c r="AA737" s="0">
         <v>4.333333333333333</v>
@@ -79291,13 +79519,34 @@
         <v>2</v>
       </c>
       <c r="E738" s="0" t="s">
-        <v>5283</v>
+        <v>5314</v>
+      </c>
+      <c r="F738" s="0" t="s">
+        <v>5315</v>
+      </c>
+      <c r="G738" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H738" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I738" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J738" s="0">
+        <v>3769882</v>
+      </c>
+      <c r="R738" s="0" t="s">
+        <v>5316</v>
+      </c>
+      <c r="S738" s="0" t="s">
+        <v>5317</v>
       </c>
       <c r="U738" s="0">
         <v>8</v>
       </c>
       <c r="V738" s="0" t="s">
-        <v>5284</v>
+        <v>5318</v>
       </c>
       <c r="W738" s="0">
         <v>8</v>
@@ -79329,10 +79578,10 @@
         <v>2</v>
       </c>
       <c r="E739" s="0" t="s">
-        <v>5285</v>
+        <v>5319</v>
       </c>
       <c r="F739" s="0" t="s">
-        <v>5286</v>
+        <v>5319</v>
       </c>
       <c r="G739" s="0" t="s">
         <v>49</v>
@@ -79341,25 +79590,34 @@
         <v>151</v>
       </c>
       <c r="I739" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
+      </c>
+      <c r="J739" s="0">
+        <v>2253701</v>
+      </c>
+      <c r="R739" s="0" t="s">
+        <v>5320</v>
+      </c>
+      <c r="S739" s="0" t="s">
+        <v>5321</v>
       </c>
       <c r="U739" s="0">
         <v>5</v>
       </c>
       <c r="V739" s="0" t="s">
-        <v>5287</v>
+        <v>5322</v>
       </c>
       <c r="W739" s="0">
         <v>5</v>
       </c>
       <c r="X739" s="0" t="s">
-        <v>5288</v>
+        <v>5323</v>
       </c>
       <c r="Y739" s="0">
         <v>2</v>
       </c>
       <c r="Z739" s="0" t="s">
-        <v>5289</v>
+        <v>5324</v>
       </c>
       <c r="AA739" s="0">
         <v>4</v>
@@ -79376,13 +79634,34 @@
         <v>2</v>
       </c>
       <c r="E740" s="0" t="s">
-        <v>5290</v>
+        <v>4474</v>
+      </c>
+      <c r="F740" s="0" t="s">
+        <v>4474</v>
+      </c>
+      <c r="G740" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H740" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I740" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J740" s="0">
+        <v>9420434</v>
+      </c>
+      <c r="R740" s="0" t="s">
+        <v>5325</v>
+      </c>
+      <c r="S740" s="0" t="s">
+        <v>4477</v>
       </c>
       <c r="U740" s="0">
         <v>7</v>
       </c>
       <c r="V740" s="0" t="s">
-        <v>5291</v>
+        <v>5326</v>
       </c>
       <c r="W740" s="0">
         <v>8</v>
@@ -79394,7 +79673,7 @@
         <v>2</v>
       </c>
       <c r="Z740" s="0" t="s">
-        <v>5289</v>
+        <v>5324</v>
       </c>
       <c r="AA740" s="0">
         <v>5.666666666666667</v>
@@ -79414,10 +79693,10 @@
         <v>2</v>
       </c>
       <c r="E741" s="0" t="s">
-        <v>5292</v>
+        <v>5327</v>
       </c>
       <c r="F741" s="0" t="s">
-        <v>5293</v>
+        <v>5328</v>
       </c>
       <c r="G741" s="0" t="s">
         <v>49</v>
@@ -79426,13 +79705,22 @@
         <v>151</v>
       </c>
       <c r="I741" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
+      </c>
+      <c r="J741" s="0">
+        <v>3845616</v>
+      </c>
+      <c r="R741" s="0" t="s">
+        <v>5329</v>
+      </c>
+      <c r="S741" s="0" t="s">
+        <v>2932</v>
       </c>
       <c r="U741" s="0">
         <v>5</v>
       </c>
       <c r="V741" s="0" t="s">
-        <v>5294</v>
+        <v>5330</v>
       </c>
       <c r="W741" s="0">
         <v>2</v>
@@ -79444,7 +79732,7 @@
         <v>4</v>
       </c>
       <c r="Z741" s="0" t="s">
-        <v>5295</v>
+        <v>5331</v>
       </c>
       <c r="AA741" s="0">
         <v>3.6666666666666665</v>
@@ -79461,48 +79749,63 @@
         <v>2</v>
       </c>
       <c r="E742" s="0" t="s">
-        <v>5296</v>
+        <v>5332</v>
+      </c>
+      <c r="F742" s="0" t="s">
+        <v>5333</v>
+      </c>
+      <c r="G742" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H742" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I742" s="0" t="s">
+        <v>5208</v>
+      </c>
+      <c r="J742" s="0">
+        <v>16649521</v>
+      </c>
+      <c r="R742" s="0" t="s">
+        <v>5334</v>
+      </c>
+      <c r="S742" s="0" t="s">
+        <v>5335</v>
       </c>
       <c r="U742" s="0">
         <v>10</v>
       </c>
       <c r="V742" s="0" t="s">
-        <v>5297</v>
+        <v>5336</v>
       </c>
       <c r="W742" s="0">
         <v>10</v>
       </c>
       <c r="X742" s="0" t="s">
-        <v>5298</v>
+        <v>5337</v>
       </c>
       <c r="Y742" s="0">
         <v>10</v>
       </c>
       <c r="Z742" s="0" t="s">
-        <v>5299</v>
+        <v>5338</v>
       </c>
       <c r="AA742" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="743">
-      <c r="A743" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="B743" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C743" s="0">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D743" s="0">
         <v>2</v>
       </c>
       <c r="E743" s="0" t="s">
-        <v>5300</v>
-      </c>
-      <c r="F743" s="0" t="s">
-        <v>5301</v>
+        <v>5339</v>
       </c>
       <c r="G743" s="0" t="s">
         <v>49</v>
@@ -79511,28 +79814,28 @@
         <v>151</v>
       </c>
       <c r="I743" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="U743" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V743" s="0" t="s">
-        <v>5302</v>
+        <v>5340</v>
       </c>
       <c r="W743" s="0">
         <v>4</v>
       </c>
       <c r="X743" s="0" t="s">
-        <v>5267</v>
+        <v>5341</v>
       </c>
       <c r="Y743" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z743" s="0" t="s">
-        <v>5303</v>
+        <v>5342</v>
       </c>
       <c r="AA743" s="0">
-        <v>5</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="744">
@@ -79540,54 +79843,57 @@
         <v>78</v>
       </c>
       <c r="C744" s="0">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D744" s="0">
         <v>2</v>
       </c>
       <c r="E744" s="0" t="s">
-        <v>5304</v>
+        <v>5343</v>
+      </c>
+      <c r="G744" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H744" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I744" s="0" t="s">
+        <v>5208</v>
       </c>
       <c r="U744" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V744" s="0" t="s">
-        <v>5305</v>
+        <v>5344</v>
       </c>
       <c r="W744" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X744" s="0" t="s">
-        <v>5306</v>
+        <v>1014</v>
       </c>
       <c r="Y744" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z744" s="0" t="s">
-        <v>5307</v>
+        <v>5345</v>
       </c>
       <c r="AA744" s="0">
-        <v>3.3333333333333335</v>
+        <v>2</v>
       </c>
     </row>
     <row r="745">
-      <c r="A745" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="B745" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C745" s="0">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D745" s="0">
         <v>2</v>
       </c>
       <c r="E745" s="0" t="s">
-        <v>5308</v>
-      </c>
-      <c r="F745" s="0" t="s">
-        <v>5309</v>
+        <v>5346</v>
       </c>
       <c r="G745" s="0" t="s">
         <v>49</v>
@@ -79596,31 +79902,28 @@
         <v>151</v>
       </c>
       <c r="I745" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J745" s="0">
-        <v>2640532</v>
+        <v>5208</v>
       </c>
       <c r="U745" s="0">
+        <v>5</v>
+      </c>
+      <c r="V745" s="0" t="s">
+        <v>5347</v>
+      </c>
+      <c r="W745" s="0">
+        <v>5</v>
+      </c>
+      <c r="X745" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="Y745" s="0">
         <v>4</v>
       </c>
-      <c r="V745" s="0" t="s">
-        <v>5310</v>
-      </c>
-      <c r="W745" s="0">
-        <v>2</v>
-      </c>
-      <c r="X745" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="Y745" s="0">
-        <v>2</v>
-      </c>
       <c r="Z745" s="0" t="s">
-        <v>5223</v>
+        <v>5313</v>
       </c>
       <c r="AA745" s="0">
-        <v>2.6666666666666665</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="746">
@@ -79628,54 +79931,57 @@
         <v>78</v>
       </c>
       <c r="C746" s="0">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D746" s="0">
         <v>2</v>
       </c>
       <c r="E746" s="0" t="s">
-        <v>5311</v>
+        <v>5348</v>
+      </c>
+      <c r="G746" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H746" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I746" s="0" t="s">
+        <v>5208</v>
       </c>
       <c r="U746" s="0">
+        <v>6</v>
+      </c>
+      <c r="V746" s="0" t="s">
+        <v>5349</v>
+      </c>
+      <c r="W746" s="0">
+        <v>5</v>
+      </c>
+      <c r="X746" s="0" t="s">
+        <v>2526</v>
+      </c>
+      <c r="Y746" s="0">
         <v>3</v>
       </c>
-      <c r="V746" s="0" t="s">
-        <v>5312</v>
-      </c>
-      <c r="W746" s="0">
-        <v>2</v>
-      </c>
-      <c r="X746" s="0" t="s">
-        <v>1014</v>
-      </c>
-      <c r="Y746" s="0">
-        <v>1</v>
-      </c>
       <c r="Z746" s="0" t="s">
-        <v>5313</v>
+        <v>5324</v>
       </c>
       <c r="AA746" s="0">
-        <v>2</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="747">
-      <c r="A747" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="B747" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C747" s="0">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="D747" s="0">
         <v>2</v>
       </c>
       <c r="E747" s="0" t="s">
-        <v>5314</v>
-      </c>
-      <c r="F747" s="0" t="s">
-        <v>5315</v>
+        <v>5350</v>
       </c>
       <c r="G747" s="0" t="s">
         <v>49</v>
@@ -79684,28 +79990,25 @@
         <v>151</v>
       </c>
       <c r="I747" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J747" s="0">
-        <v>14622517</v>
+        <v>5208</v>
       </c>
       <c r="U747" s="0">
         <v>8</v>
       </c>
       <c r="V747" s="0" t="s">
-        <v>5316</v>
+        <v>5351</v>
       </c>
       <c r="W747" s="0">
         <v>8</v>
       </c>
       <c r="X747" s="0" t="s">
-        <v>3116</v>
+        <v>5352</v>
       </c>
       <c r="Y747" s="0">
         <v>8</v>
       </c>
       <c r="Z747" s="0" t="s">
-        <v>5317</v>
+        <v>5187</v>
       </c>
       <c r="AA747" s="0">
         <v>8</v>
@@ -79716,54 +80019,57 @@
         <v>78</v>
       </c>
       <c r="C748" s="0">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D748" s="0">
         <v>2</v>
       </c>
       <c r="E748" s="0" t="s">
-        <v>5318</v>
+        <v>5353</v>
+      </c>
+      <c r="G748" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H748" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I748" s="0" t="s">
+        <v>5208</v>
       </c>
       <c r="U748" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V748" s="0" t="s">
-        <v>5319</v>
+        <v>5354</v>
       </c>
       <c r="W748" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X748" s="0" t="s">
-        <v>836</v>
+        <v>5355</v>
       </c>
       <c r="Y748" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z748" s="0" t="s">
-        <v>5282</v>
+        <v>5356</v>
       </c>
       <c r="AA748" s="0">
-        <v>4.666666666666667</v>
+        <v>8</v>
       </c>
     </row>
     <row r="749">
-      <c r="A749" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="B749" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C749" s="0">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="D749" s="0">
         <v>2</v>
       </c>
       <c r="E749" s="0" t="s">
-        <v>5320</v>
-      </c>
-      <c r="F749" s="0" t="s">
-        <v>5321</v>
+        <v>5357</v>
       </c>
       <c r="G749" s="0" t="s">
         <v>49</v>
@@ -79772,28 +80078,28 @@
         <v>151</v>
       </c>
       <c r="I749" s="0" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="U749" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V749" s="0" t="s">
-        <v>5322</v>
+        <v>5358</v>
       </c>
       <c r="W749" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X749" s="0" t="s">
-        <v>1014</v>
+        <v>5359</v>
       </c>
       <c r="Y749" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z749" s="0" t="s">
-        <v>5313</v>
+        <v>5360</v>
       </c>
       <c r="AA749" s="0">
-        <v>2.3333333333333335</v>
+        <v>7.666666666666667</v>
       </c>
     </row>
     <row r="750">
@@ -79801,54 +80107,57 @@
         <v>78</v>
       </c>
       <c r="C750" s="0">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="D750" s="0">
         <v>2</v>
       </c>
       <c r="E750" s="0" t="s">
-        <v>5323</v>
+        <v>5361</v>
+      </c>
+      <c r="G750" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H750" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I750" s="0" t="s">
+        <v>5208</v>
       </c>
       <c r="U750" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V750" s="0" t="s">
-        <v>5324</v>
+        <v>5362</v>
       </c>
       <c r="W750" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X750" s="0" t="s">
-        <v>2526</v>
+        <v>3196</v>
       </c>
       <c r="Y750" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Z750" s="0" t="s">
-        <v>5289</v>
+        <v>5363</v>
       </c>
       <c r="AA750" s="0">
-        <v>4.666666666666667</v>
+        <v>7.666666666666667</v>
       </c>
     </row>
     <row r="751">
-      <c r="A751" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="B751" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C751" s="0">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="D751" s="0">
         <v>2</v>
       </c>
       <c r="E751" s="0" t="s">
-        <v>5325</v>
-      </c>
-      <c r="F751" s="0" t="s">
-        <v>5326</v>
+        <v>5364</v>
       </c>
       <c r="G751" s="0" t="s">
         <v>49</v>
@@ -79857,66 +80166,78 @@
         <v>151</v>
       </c>
       <c r="I751" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J751" s="0">
-        <v>7031219</v>
+        <v>5208</v>
       </c>
       <c r="U751" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V751" s="0" t="s">
-        <v>5327</v>
+        <v>5365</v>
       </c>
       <c r="W751" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X751" s="0" t="s">
-        <v>5328</v>
+        <v>5366</v>
       </c>
       <c r="Y751" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z751" s="0" t="s">
-        <v>5121</v>
+        <v>5367</v>
       </c>
       <c r="AA751" s="0">
-        <v>3.3333333333333335</v>
+        <v>8.6666666666666661</v>
       </c>
     </row>
     <row r="752">
+      <c r="A752" s="0" t="s">
+        <v>46</v>
+      </c>
       <c r="B752" s="0" t="s">
         <v>78</v>
       </c>
       <c r="C752" s="0">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="D752" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E752" s="0" t="s">
-        <v>5329</v>
+        <v>5368</v>
+      </c>
+      <c r="F752" s="0" t="s">
+        <v>5368</v>
+      </c>
+      <c r="G752" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="H752" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I752" s="0" t="s">
+        <v>5369</v>
       </c>
       <c r="U752" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V752" s="0" t="s">
-        <v>5330</v>
+        <v>5370</v>
       </c>
       <c r="W752" s="0">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X752" s="0" t="s">
-        <v>5331</v>
+        <v>305</v>
       </c>
       <c r="Y752" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z752" s="0" t="s">
-        <v>5187</v>
+        <v>5371</v>
       </c>
       <c r="AA752" s="0">
-        <v>8</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="753">
@@ -79924,951 +80245,152 @@
         <v>46</v>
       </c>
       <c r="B753" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C753" s="0">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="D753" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E753" s="0" t="s">
-        <v>5332</v>
+        <v>5372</v>
       </c>
       <c r="F753" s="0" t="s">
-        <v>5333</v>
+        <v>5372</v>
       </c>
       <c r="G753" s="0" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="H753" s="0" t="s">
-        <v>151</v>
+        <v>494</v>
       </c>
       <c r="I753" s="0" t="s">
-        <v>5209</v>
+        <v>5373</v>
+      </c>
+      <c r="J753" s="0">
+        <v>15508595</v>
+      </c>
+      <c r="K753" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="R753" s="0" t="s">
+        <v>3276</v>
+      </c>
+      <c r="S753" s="0" t="s">
+        <v>3277</v>
       </c>
       <c r="U753" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V753" s="0" t="s">
-        <v>5334</v>
+        <v>5374</v>
       </c>
       <c r="W753" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X753" s="0" t="s">
-        <v>5335</v>
+        <v>3206</v>
       </c>
       <c r="Y753" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Z753" s="0" t="s">
-        <v>5223</v>
+        <v>5375</v>
       </c>
       <c r="AA753" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="754">
+      <c r="A754" s="0" t="s">
+        <v>46</v>
+      </c>
       <c r="B754" s="0" t="s">
         <v>78</v>
       </c>
       <c r="C754" s="0">
-        <v>755</v>
+        <v>772</v>
       </c>
       <c r="D754" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E754" s="0" t="s">
-        <v>5336</v>
+        <v>5376</v>
+      </c>
+      <c r="F754" s="0" t="s">
+        <v>5377</v>
+      </c>
+      <c r="G754" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="H754" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="I754" s="0" t="s">
+        <v>5378</v>
+      </c>
+      <c r="J754" s="0">
+        <v>8786229</v>
+      </c>
+      <c r="K754" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q754" s="0" t="s">
+        <v>5379</v>
+      </c>
+      <c r="R754" s="0" t="s">
+        <v>5380</v>
+      </c>
+      <c r="S754" s="0" t="s">
+        <v>5381</v>
       </c>
       <c r="U754" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V754" s="0" t="s">
-        <v>5337</v>
+        <v>5382</v>
       </c>
       <c r="W754" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X754" s="0" t="s">
-        <v>5338</v>
+        <v>84</v>
       </c>
       <c r="Y754" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z754" s="0" t="s">
-        <v>5317</v>
+        <v>5342</v>
       </c>
       <c r="AA754" s="0">
-        <v>8</v>
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="755">
-      <c r="A755" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="B755" s="0" t="s">
-        <v>5206</v>
+        <v>78</v>
       </c>
       <c r="C755" s="0">
-        <v>756</v>
+        <v>773</v>
       </c>
       <c r="D755" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E755" s="0" t="s">
-        <v>5339</v>
+        <v>1515</v>
       </c>
       <c r="F755" s="0" t="s">
-        <v>3262</v>
+        <v>1515</v>
       </c>
       <c r="G755" s="0" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="H755" s="0" t="s">
-        <v>151</v>
+        <v>5383</v>
       </c>
       <c r="I755" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="U755" s="0">
-        <v>7</v>
-      </c>
-      <c r="V755" s="0" t="s">
-        <v>5340</v>
-      </c>
-      <c r="W755" s="0">
-        <v>7</v>
-      </c>
-      <c r="X755" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y755" s="0">
-        <v>6</v>
-      </c>
-      <c r="Z755" s="0" t="s">
-        <v>5341</v>
-      </c>
-      <c r="AA755" s="0">
-        <v>6.666666666666667</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="B756" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C756" s="0">
-        <v>757</v>
-      </c>
-      <c r="D756" s="0">
-        <v>2</v>
-      </c>
-      <c r="E756" s="0" t="s">
-        <v>5342</v>
-      </c>
-      <c r="U756" s="0">
-        <v>8</v>
-      </c>
-      <c r="V756" s="0" t="s">
-        <v>5343</v>
-      </c>
-      <c r="W756" s="0">
-        <v>7</v>
-      </c>
-      <c r="X756" s="0" t="s">
-        <v>5344</v>
-      </c>
-      <c r="Y756" s="0">
-        <v>8</v>
-      </c>
-      <c r="Z756" s="0" t="s">
-        <v>5345</v>
-      </c>
-      <c r="AA756" s="0">
-        <v>7.666666666666667</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B757" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C757" s="0">
-        <v>758</v>
-      </c>
-      <c r="D757" s="0">
-        <v>2</v>
-      </c>
-      <c r="E757" s="0" t="s">
-        <v>5346</v>
-      </c>
-      <c r="F757" s="0" t="s">
-        <v>5347</v>
-      </c>
-      <c r="G757" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H757" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I757" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J757" s="0">
-        <v>2605046</v>
-      </c>
-      <c r="U757" s="0">
-        <v>5</v>
-      </c>
-      <c r="V757" s="0" t="s">
-        <v>5348</v>
-      </c>
-      <c r="W757" s="0">
-        <v>4</v>
-      </c>
-      <c r="X757" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="Y757" s="0">
-        <v>4</v>
-      </c>
-      <c r="Z757" s="0" t="s">
-        <v>5260</v>
-      </c>
-      <c r="AA757" s="0">
-        <v>4.333333333333333</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="B758" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C758" s="0">
-        <v>759</v>
-      </c>
-      <c r="D758" s="0">
-        <v>2</v>
-      </c>
-      <c r="E758" s="0" t="s">
-        <v>5349</v>
-      </c>
-      <c r="U758" s="0">
-        <v>8</v>
-      </c>
-      <c r="V758" s="0" t="s">
-        <v>5350</v>
-      </c>
-      <c r="W758" s="0">
-        <v>7</v>
-      </c>
-      <c r="X758" s="0" t="s">
-        <v>3196</v>
-      </c>
-      <c r="Y758" s="0">
-        <v>8</v>
-      </c>
-      <c r="Z758" s="0" t="s">
-        <v>5351</v>
-      </c>
-      <c r="AA758" s="0">
-        <v>7.666666666666667</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B759" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C759" s="0">
-        <v>760</v>
-      </c>
-      <c r="D759" s="0">
-        <v>2</v>
-      </c>
-      <c r="E759" s="0" t="s">
-        <v>5352</v>
-      </c>
-      <c r="F759" s="0" t="s">
-        <v>5353</v>
-      </c>
-      <c r="G759" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H759" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I759" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="U759" s="0">
-        <v>7</v>
-      </c>
-      <c r="V759" s="0" t="s">
-        <v>5354</v>
-      </c>
-      <c r="W759" s="0">
-        <v>7</v>
-      </c>
-      <c r="X759" s="0" t="s">
-        <v>3433</v>
-      </c>
-      <c r="Y759" s="0">
-        <v>7</v>
-      </c>
-      <c r="Z759" s="0" t="s">
-        <v>5355</v>
-      </c>
-      <c r="AA759" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="B760" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C760" s="0">
-        <v>761</v>
-      </c>
-      <c r="D760" s="0">
-        <v>2</v>
-      </c>
-      <c r="E760" s="0" t="s">
-        <v>5356</v>
-      </c>
-      <c r="U760" s="0">
-        <v>9</v>
-      </c>
-      <c r="V760" s="0" t="s">
-        <v>5357</v>
-      </c>
-      <c r="W760" s="0">
-        <v>8</v>
-      </c>
-      <c r="X760" s="0" t="s">
-        <v>5358</v>
-      </c>
-      <c r="Y760" s="0">
-        <v>9</v>
-      </c>
-      <c r="Z760" s="0" t="s">
-        <v>5359</v>
-      </c>
-      <c r="AA760" s="0">
-        <v>8.6666666666666661</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B761" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C761" s="0">
-        <v>762</v>
-      </c>
-      <c r="D761" s="0">
-        <v>2</v>
-      </c>
-      <c r="E761" s="0" t="s">
-        <v>5360</v>
-      </c>
-      <c r="F761" s="0" t="s">
-        <v>5361</v>
-      </c>
-      <c r="G761" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H761" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I761" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J761" s="0">
-        <v>14249828</v>
-      </c>
-      <c r="U761" s="0">
-        <v>4</v>
-      </c>
-      <c r="V761" s="0" t="s">
-        <v>5362</v>
-      </c>
-      <c r="W761" s="0">
-        <v>3</v>
-      </c>
-      <c r="X761" s="0" t="s">
-        <v>5363</v>
-      </c>
-      <c r="Y761" s="0">
-        <v>2</v>
-      </c>
-      <c r="Z761" s="0" t="s">
-        <v>5364</v>
-      </c>
-      <c r="AA761" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B762" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C762" s="0">
-        <v>763</v>
-      </c>
-      <c r="D762" s="0">
-        <v>1</v>
-      </c>
-      <c r="E762" s="0" t="s">
-        <v>5365</v>
-      </c>
-      <c r="F762" s="0" t="s">
-        <v>5365</v>
-      </c>
-      <c r="G762" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="H762" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I762" s="0" t="s">
-        <v>5366</v>
-      </c>
-      <c r="U762" s="0">
-        <v>5</v>
-      </c>
-      <c r="V762" s="0" t="s">
-        <v>5367</v>
-      </c>
-      <c r="W762" s="0">
-        <v>4</v>
-      </c>
-      <c r="X762" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="Y762" s="0">
-        <v>5</v>
-      </c>
-      <c r="Z762" s="0" t="s">
-        <v>5368</v>
-      </c>
-      <c r="AA762" s="0">
-        <v>4.666666666666667</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B763" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C763" s="0">
-        <v>764</v>
-      </c>
-      <c r="D763" s="0">
-        <v>2</v>
-      </c>
-      <c r="E763" s="0" t="s">
-        <v>5369</v>
-      </c>
-      <c r="F763" s="0" t="s">
-        <v>5370</v>
-      </c>
-      <c r="G763" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H763" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I763" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J763" s="0">
-        <v>3968273</v>
-      </c>
-      <c r="U763" s="0">
-        <v>6</v>
-      </c>
-      <c r="V763" s="0" t="s">
-        <v>3583</v>
-      </c>
-      <c r="W763" s="0">
-        <v>5</v>
-      </c>
-      <c r="X763" s="0" t="s">
-        <v>632</v>
-      </c>
-      <c r="Y763" s="0">
-        <v>6</v>
-      </c>
-      <c r="Z763" s="0" t="s">
-        <v>5371</v>
-      </c>
-      <c r="AA763" s="0">
-        <v>5.666666666666667</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B764" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C764" s="0">
-        <v>765</v>
-      </c>
-      <c r="D764" s="0">
-        <v>1</v>
-      </c>
-      <c r="E764" s="0" t="s">
-        <v>5372</v>
-      </c>
-      <c r="F764" s="0" t="s">
-        <v>5372</v>
-      </c>
-      <c r="G764" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="H764" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="I764" s="0" t="s">
-        <v>5373</v>
-      </c>
-      <c r="J764" s="0">
-        <v>15508595</v>
-      </c>
-      <c r="K764" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="R764" s="0" t="s">
-        <v>3276</v>
-      </c>
-      <c r="S764" s="0" t="s">
-        <v>3277</v>
-      </c>
-      <c r="U764" s="0">
-        <v>9</v>
-      </c>
-      <c r="V764" s="0" t="s">
-        <v>5374</v>
-      </c>
-      <c r="W764" s="0">
-        <v>9</v>
-      </c>
-      <c r="X764" s="0" t="s">
-        <v>3206</v>
-      </c>
-      <c r="Y764" s="0">
-        <v>9</v>
-      </c>
-      <c r="Z764" s="0" t="s">
-        <v>5375</v>
-      </c>
-      <c r="AA764" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B765" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C765" s="0">
-        <v>766</v>
-      </c>
-      <c r="D765" s="0">
-        <v>2</v>
-      </c>
-      <c r="E765" s="0" t="s">
-        <v>5376</v>
-      </c>
-      <c r="F765" s="0" t="s">
-        <v>5377</v>
-      </c>
-      <c r="G765" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H765" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I765" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="U765" s="0">
-        <v>8</v>
-      </c>
-      <c r="V765" s="0" t="s">
-        <v>5378</v>
-      </c>
-      <c r="W765" s="0">
-        <v>6</v>
-      </c>
-      <c r="X765" s="0" t="s">
-        <v>3659</v>
-      </c>
-      <c r="Y765" s="0">
-        <v>3</v>
-      </c>
-      <c r="Z765" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA765" s="0">
-        <v>5.666666666666667</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B766" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C766" s="0">
-        <v>767</v>
-      </c>
-      <c r="D766" s="0">
-        <v>2</v>
-      </c>
-      <c r="E766" s="0" t="s">
-        <v>5379</v>
-      </c>
-      <c r="F766" s="0" t="s">
-        <v>5380</v>
-      </c>
-      <c r="G766" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H766" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I766" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="U766" s="0">
-        <v>3</v>
-      </c>
-      <c r="V766" s="0" t="s">
-        <v>5381</v>
-      </c>
-      <c r="W766" s="0">
-        <v>2</v>
-      </c>
-      <c r="X766" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="Y766" s="0">
-        <v>1</v>
-      </c>
-      <c r="Z766" s="0" t="s">
-        <v>5223</v>
-      </c>
-      <c r="AA766" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B767" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C767" s="0">
-        <v>768</v>
-      </c>
-      <c r="D767" s="0">
-        <v>2</v>
-      </c>
-      <c r="E767" s="0" t="s">
-        <v>5382</v>
-      </c>
-      <c r="F767" s="0" t="s">
-        <v>5383</v>
-      </c>
-      <c r="G767" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H767" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I767" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J767" s="0">
-        <v>2253701</v>
-      </c>
-      <c r="U767" s="0">
-        <v>4</v>
-      </c>
-      <c r="V767" s="0" t="s">
         <v>5384</v>
-      </c>
-      <c r="W767" s="0">
-        <v>2</v>
-      </c>
-      <c r="X767" s="0" t="s">
-        <v>4816</v>
-      </c>
-      <c r="Y767" s="0">
-        <v>1</v>
-      </c>
-      <c r="Z767" s="0" t="s">
-        <v>5205</v>
-      </c>
-      <c r="AA767" s="0">
-        <v>2.3333333333333335</v>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B768" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C768" s="0">
-        <v>769</v>
-      </c>
-      <c r="D768" s="0">
-        <v>2</v>
-      </c>
-      <c r="E768" s="0" t="s">
-        <v>5385</v>
-      </c>
-      <c r="F768" s="0" t="s">
-        <v>4474</v>
-      </c>
-      <c r="G768" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H768" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I768" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="J768" s="0">
-        <v>9420434</v>
-      </c>
-      <c r="U768" s="0">
-        <v>5</v>
-      </c>
-      <c r="V768" s="0" t="s">
-        <v>5386</v>
-      </c>
-      <c r="W768" s="0">
-        <v>4</v>
-      </c>
-      <c r="X768" s="0" t="s">
-        <v>1014</v>
-      </c>
-      <c r="Y768" s="0">
-        <v>6</v>
-      </c>
-      <c r="Z768" s="0" t="s">
-        <v>5387</v>
-      </c>
-      <c r="AA768" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B769" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C769" s="0">
-        <v>770</v>
-      </c>
-      <c r="D769" s="0">
-        <v>2</v>
-      </c>
-      <c r="E769" s="0" t="s">
-        <v>5388</v>
-      </c>
-      <c r="F769" s="0" t="s">
-        <v>5389</v>
-      </c>
-      <c r="G769" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H769" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I769" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="U769" s="0">
-        <v>7</v>
-      </c>
-      <c r="V769" s="0" t="s">
-        <v>5390</v>
-      </c>
-      <c r="W769" s="0">
-        <v>7</v>
-      </c>
-      <c r="X769" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y769" s="0">
-        <v>6</v>
-      </c>
-      <c r="Z769" s="0" t="s">
-        <v>5391</v>
-      </c>
-      <c r="AA769" s="0">
-        <v>6.666666666666667</v>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B770" s="0" t="s">
-        <v>5206</v>
-      </c>
-      <c r="C770" s="0">
-        <v>771</v>
-      </c>
-      <c r="D770" s="0">
-        <v>2</v>
-      </c>
-      <c r="E770" s="0" t="s">
-        <v>5392</v>
-      </c>
-      <c r="F770" s="0" t="s">
-        <v>5393</v>
-      </c>
-      <c r="G770" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H770" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I770" s="0" t="s">
-        <v>5209</v>
-      </c>
-      <c r="U770" s="0">
-        <v>6</v>
-      </c>
-      <c r="V770" s="0" t="s">
-        <v>5394</v>
-      </c>
-      <c r="W770" s="0">
-        <v>5</v>
-      </c>
-      <c r="X770" s="0" t="s">
-        <v>5395</v>
-      </c>
-      <c r="Y770" s="0">
-        <v>5</v>
-      </c>
-      <c r="Z770" s="0" t="s">
-        <v>5254</v>
-      </c>
-      <c r="AA770" s="0">
-        <v>5.333333333333333</v>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C771" s="0">
-        <v>772</v>
-      </c>
-      <c r="D771" s="0">
-        <v>1</v>
-      </c>
-      <c r="E771" s="0" t="s">
-        <v>5396</v>
-      </c>
-      <c r="F771" s="0" t="s">
-        <v>5397</v>
-      </c>
-      <c r="G771" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="H771" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="I771" s="0" t="s">
-        <v>5398</v>
-      </c>
-      <c r="J771" s="0">
-        <v>8786229</v>
-      </c>
-      <c r="K771" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q771" s="0" t="s">
-        <v>5399</v>
-      </c>
-      <c r="R771" s="0" t="s">
-        <v>5400</v>
-      </c>
-      <c r="S771" s="0" t="s">
-        <v>5401</v>
-      </c>
-      <c r="U771" s="0">
-        <v>5</v>
-      </c>
-      <c r="V771" s="0" t="s">
-        <v>5402</v>
-      </c>
-      <c r="W771" s="0">
-        <v>6</v>
-      </c>
-      <c r="X771" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y771" s="0">
-        <v>2</v>
-      </c>
-      <c r="Z771" s="0" t="s">
-        <v>5307</v>
-      </c>
-      <c r="AA771" s="0">
-        <v>4.333333333333333</v>
-      </c>
-    </row>
-    <row r="772">
-      <c r="C772" s="0">
-        <v>773</v>
-      </c>
-      <c r="D772" s="0">
-        <v>1</v>
-      </c>
-      <c r="E772" s="0" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F772" s="0" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G772" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="H772" s="0" t="s">
-        <v>5403</v>
-      </c>
-      <c r="I772" s="0" t="s">
-        <v>5404</v>
       </c>
     </row>
   </sheetData>

--- a/attached_assets/Portal_Data_Latest.xlsx
+++ b/attached_assets/Portal_Data_Latest.xlsx
@@ -4515,10 +4515,10 @@
     <t>03/11 - Tracking down best contact</t>
   </si>
   <si>
-    <t>The Greenway, Crusoe Ai, Block C, Ardilaun Court,, 112-114 St Stephen's Green,, Dublin 2,, Dublin, D02 Td28, Ireland</t>
-  </si>
-  <si>
-    <t>DUBLIN</t>
+    <t>The Greenway, Crusoe Ai, Block C, Ardilaun Court, 112-114 St Stephen's Green, Dublin 2, Dublin, D02 Td28, Ireland</t>
+  </si>
+  <si>
+    <t>D02 Td28</t>
   </si>
   <si>
     <t>A company focused on using stranded energy for high-performance computing, ideal for AI training.</t>

--- a/attached_assets/Portal_Data_Latest.xlsx
+++ b/attached_assets/Portal_Data_Latest.xlsx
@@ -7657,7 +7657,7 @@
     <t>GCORE TECHNOLOGIES UK LIMITED</t>
   </si>
   <si>
-    <t>03/11 - Customer meeting, generating playbooks, followup on the 10/11</t>
+    <t>19/11 - Customer meeting review playbooks and campaign</t>
   </si>
   <si>
     <t>www.gcore.com</t>
